--- a/public/管理口径原因分析默认模版/浙江项目部.xlsx
+++ b/public/管理口径原因分析默认模版/浙江项目部.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="218">
   <si>
     <t>工作表目录</t>
   </si>
@@ -148,7 +148,7 @@
     <t>浙江衢州销售分公司配餐劳务项目</t>
   </si>
   <si>
-    <t>合计预算执行分析（2026年07月）</t>
+    <t>合计预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目</t>
@@ -370,8 +370,8 @@
     <t>二、利润总额</t>
   </si>
   <si>
-    <t xml:space="preserve">1-7月浙江项目部实现营业收入994.07万元，完成进度预算989.1万元的100.5%。四个业务板块中，除餐饮业务外，均完成进度预算。1-7月浙江项目部营业收入较上年同期756.83万元增加237.24万元，租赁业务收入同比下降，主要系本年度多一个月免租期所致，其它三个业务版块同比均有增加，其中增幅最大为物业业务96.51万元。
-1-7月浙江项目部实现净利润152.84万元，完成进度预算103.25万元的148.03％，除餐业务外均有不同幅度增加。其中完成进度利润预算项目10个、未完成4个。1-7月浙江项目部净利润152.84万元，较2025年同期152.77万元增加0.07万元。其中，租赁业务利润较同期减少46.83万元，其它13个项目利润均有增加。</t>
+    <t xml:space="preserve">1-8月浙江项目部实现营业收入1132.23万元，完成进度预算989.1万元的100.14%。四个业务板块中，除餐饮业务外，均完成进度预算。1-8月浙江项目部营业收入较上年同期917.87万元增加214.36万元，租赁业务收入同比下降，主要系本年度多一个月免租期所致，其它三个业务版块同比均有增加，其中增幅最大为物业业务105.22万元。
+1-8月浙江项目部实现净利润178.65万元，完成进度预算117.73万元的151.75％，除餐业务外均有不同幅度增加。其中完成进度利润预算项目11个、未完成5个。1-8月浙江项目部净利润178.65万元，较2025年同期179.07万元减少0.42万元。其中，租赁业务利润较同期减少56.37万元，其它13个项目利润均有增加。</t>
   </si>
   <si>
     <t>三、所得税费用</t>
@@ -380,10 +380,10 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>浙江销售分公司配餐业务预算执行分析（2026年07月）</t>
+    <t>浙江销售分公司配餐业务预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>1-7月销售收入比同期有增长</t>
+    <t>1-8月销售收入比同期有增长</t>
   </si>
   <si>
     <t>桌餐增加，员工加班费增加及食材成本增加福利套餐，成本费用相对增加</t>
@@ -404,10 +404,10 @@
     <t>去年同期有差旅费用今年无</t>
   </si>
   <si>
-    <t>1-7月销售收入比同期有增长，成本相应有增加，利润有所增加，主要原因1、2月份及5月份发放甲方团购福利套餐，食材成本费用相对增加。2.春节前应甲方要求开展美食节，用餐人数增加，造成食材成本费用增加。3.后续严格管控食材成本，降本增效，提升对标利润率。此项目为季度结算，4-7度收入为预估收入，与实际结算有出入。</t>
+    <t>1-8月销售收入比同期有增长，成本相应有增加，利润有所增加，主要原因1、2月份及5月份发放甲方团购福利套餐，食材成本费用相对增加。2.春节前应甲方要求开展美食节，用餐人数增加，造成食材成本费用增加。3.后续严格管控食材成本，降本增效，提升对标利润率。此项目为季度结算，7-8月收入为预估收入，与实际结算有出入。</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_合并预算执行分析（2026年07月）</t>
+    <t>浙江湖州销售分公司配餐业务_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>完成进度预算</t>
@@ -428,22 +428,22 @@
     <t>正常的商旅服务费核算</t>
   </si>
   <si>
-    <t>1-7月销售收入小幅增长，成本基本持平，导致利润也相应有所增加，其原因为：浙江湖州销售分公司配餐业务0031停掉后只经营劳务业务，故减少。</t>
+    <t>1-8月销售收入小幅增长，成本基本持平，导致利润也相应有所增加，其原因为：浙江湖州销售分公司配餐业务0031停掉后只经营劳务业务，故减少。</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_222200150510预算执行分析（2026年07月）</t>
+    <t>浙江湖州销售分公司配餐业务_222200150510预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_222200150542预算执行分析（2026年07月）</t>
+    <t>浙江湖州销售分公司配餐业务_222200150542预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_SH3B26Z001预算执行分析（2026年07月）</t>
+    <t>浙江湖州销售分公司配餐业务_SH3B26Z001预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_合并预算执行分析（2026年07月）</t>
+    <t>浙江杭州销售分公司劳务输出_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>此项目为季度结算，二季度收入为预估收入，比去年同期有所增加</t>
+    <t>此项目为季度结算，7-8月收入为预估收入，比去年同期有所增加</t>
   </si>
   <si>
     <t>本年度该项改为外包劳务支出</t>
@@ -455,16 +455,16 @@
     <t>去年同期有出差费用今年无</t>
   </si>
   <si>
-    <t>1-7月收入较同期有所增加，成本有所减少。利润有所增加，主要原因是收入增加</t>
+    <t>1-8月收入较同期有所增加，成本有所减少。利润有所增加，主要原因是收入增加</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_222200150526预算执行分析（2026年07月）</t>
+    <t>浙江杭州销售分公司劳务输出_222200150526预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_SH3B25Z076预算执行分析（2026年07月）</t>
+    <t>浙江杭州销售分公司劳务输出_SH3B25Z076预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_合并预算执行分析（2026年07月）</t>
+    <t>东北销售浙江宁波分公司配餐业务_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>今年用餐人数增加收入有所增加，食材费用随之增加，与该项目据实结算。</t>
@@ -473,16 +473,19 @@
     <t>用餐人数增加，食材费用随之增加</t>
   </si>
   <si>
-    <t>该项目1-7月收入比去年同期有所增加，同时成本却比去年同期期有所增加，故利润有所增加，正常核算</t>
+    <t>该项目1-8月收入比去年同期有所增加，同时成本却比去年同期期有所增加，故利润有所增加，正常核算</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_222200150527预算执行分析（2026年07月）</t>
+    <t>东北销售浙江宁波分公司配餐业务_222200150527预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_SH3B26Z005预算执行分析（2026年07月）</t>
+    <t>需要和常州合并来分析</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_合并预算执行分析（2026年07月）</t>
+    <t>东北销售浙江宁波分公司配餐业务_SH3B26Z005预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>东北销售浙江宁波分公司办公物业_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>合同的物业费增加，故收入有所增加</t>
@@ -494,19 +497,22 @@
     <t>员工全年上班，产生节假日加班费</t>
   </si>
   <si>
-    <t>该项目1-7月收入，成本，利润有小幅增长。</t>
+    <t>去年同期有出差费用今年也有，正常核算</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_222200150530预算执行分析（2026年07月）</t>
+    <t>该项目1-8月收入，成本，利润有小幅增长。</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_SH3B26Z006预算执行分析（2026年07月）</t>
+    <t>东北销售浙江宁波分公司办公物业_222200150530预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>东北销售浙江宁波分公司办公物业_SH3B26Z006预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>已达标，继续保持</t>
   </si>
   <si>
-    <t>浙江杭州地质研究院办公物业项目预算执行分析（2026年07月）</t>
+    <t>浙江杭州地质研究院办公物业项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>物业费增加以及延展服务增加，且收入增加</t>
@@ -518,10 +524,10 @@
     <t>去年同期有，今年无</t>
   </si>
   <si>
-    <t>该项目部1-7月收入较去年同期大幅增加，利润也相应大幅增加主要原因为，今年1-7月的人工成本较去年小幅增长，但收入相应增加了许多。故利润有大幅增加。</t>
+    <t>该项目部1-8月收入较去年同期大幅增加，利润也相应大幅增加主要原因为，今年1-8月的人工成本较去年小幅增长，但收入相应增加了许多。故利润有大幅增加。</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_合并预算执行分析（2026年07月）</t>
+    <t>中石化天然气分公司浙江销售配餐项目_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>与去年同期相比。收入有小幅增加，目前运行稳定</t>
@@ -536,19 +542,19 @@
     <t>去年有无零星费用发生，今年零星费用发生</t>
   </si>
   <si>
-    <t>该项目1-7月利润上升的原因，主要是今年1-7月，人工成本有所减少</t>
+    <t>该项目1-8月利润上升的原因，主要是今年1-7月，人工成本有所减少</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_222200150535预算执行分析（2026年07月）</t>
+    <t>中石化天然气分公司浙江销售配餐项目_222200150535预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_SH3B26Z002预算执行分析（2026年07月）</t>
+    <t>中石化天然气分公司浙江销售配餐项目_SH3B26Z002预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江杭州地质研究院配餐项目预算执行分析（2026年07月）</t>
+    <t>浙江杭州地质研究院配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>主要原因是收支结算周期不同导致，又因该项目是薪酬制，业主方力求服务好员工，故而压缩餐饮合同利润空间，所有损失在物业合同弥补。截止7月份末，餐卡余额同比增加，也影响本期利润。</t>
+    <t>主要原因是收支结算周期不同导致，又因该项目是薪酬制，业主方力求服务好员工，故而压缩餐饮合同利润空间，所有损失在物业合同弥补。截止8月份末，餐卡余额同比增加，也影响本期利润。</t>
   </si>
   <si>
     <t>业主方力求服务好员工，故而压缩餐饮合同利润空间，所有损失在物业合同弥补。</t>
@@ -563,40 +569,52 @@
     <t>正常的商旅费用核算</t>
   </si>
   <si>
-    <t>主要原因是收支结算周期不同导致，又因该项目是薪酬制，业主方力求服务好员工，故而压缩餐饮合同利润空间，所有损失在物业合同弥补。截止7月份末，餐卡余额同比增加，也影响本期利润。较去年同期有所增加</t>
+    <t>主要原因是收支结算周期不同导致，又因该项目是薪酬制，业主方力求服务好员工，故而压缩餐饮合同利润空间，所有损失在物业合同弥补。截止8月份末，餐卡余额同比增加，也影响本期利润。较去年同期有所增加</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_合并预算执行分析（2026年07月）</t>
+    <t>浙江绍兴销售分公司配餐劳务输出项目_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>与上期基本平行，收入有小幅增加，运行稳定</t>
   </si>
   <si>
-    <t>该项目1-7月收入、成本、利润与去年同期有小幅增加，已达标，继续保持</t>
+    <t>正常核算，本年无，同期有差旅费</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_222200150540预算执行分析（2026年07月）</t>
+    <t>该项目1-8月收入、成本、利润与去年同期有小幅增加，已达标，继续保持</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_SH3B26Z008预算执行分析（2026年07月）</t>
+    <t>浙江绍兴销售分公司配餐劳务输出项目_222200150540预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_合并预算执行分析（2026年07月）</t>
+    <t>与上期基本平行，收入有小幅减少需要同常州合并来分析，运行稳定</t>
+  </si>
+  <si>
+    <t>该项目1-8月收入、成本、利润与去年同期有小幅减少，需要 和常州核算合并来分析</t>
+  </si>
+  <si>
+    <t>浙江绍兴销售分公司配餐劳务输出项目_SH3B26Z008预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>浙江金华销售分公司配餐劳务输出项目_合并预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>超过进度预算，加班费收入有所增加</t>
   </si>
   <si>
     <t>完成进度预算，加班费收入有所增加</t>
   </si>
   <si>
-    <t>该项目1-7月收入、成本、利润与去年同期收入有所增加，主要是人工成本有所增加</t>
+    <t>该项目1-8月收入、成本、利润与去年同期收入有所增加，主要是人工成本有所增加</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_222200150541预算执行分析（2026年07月）</t>
+    <t>浙江金华销售分公司配餐劳务输出项目_222200150541预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_SH3B26Z004预算执行分析（2026年07月）</t>
+    <t>浙江金华销售分公司配餐劳务输出项目_SH3B26Z004预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>黄山阳光酒店分公司预算执行分析（2026年07月）</t>
+    <t>黄山阳光酒店分公司预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>今年免租期较同期增加1个月，收入有所减少。</t>
@@ -605,10 +623,10 @@
     <t>上半年严控成本支出</t>
   </si>
   <si>
-    <t>1-7月严控成本支出车辆燃油费等实际发生较预算减少。</t>
+    <t>1-8月严控成本支出车辆燃油费等实际发生较预算减少。</t>
   </si>
   <si>
-    <t>1-7严控成本支出车辆燃油费等实际发生较预算减少。</t>
+    <t>1-8严控成本支出车辆燃油费等实际发生较预算减少。</t>
   </si>
   <si>
     <t>暂未发生</t>
@@ -650,7 +668,7 @@
     <t>利润减少原因：收入方面今年免租期较同期增加1个月，收入减少。成本方面1.房产税按从价方式计征较去年多1个月，增加成本约13万；2.相关人员下沉人工成本增加。</t>
   </si>
   <si>
-    <t>黄山项目部销售项目预算执行分析（2026年07月）</t>
+    <t>黄山项目部销售项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>因销售具有不确定性，今年客户增加，销售额有所提升。</t>
@@ -677,10 +695,10 @@
     <t>销售提成款</t>
   </si>
   <si>
-    <t>产品销售业务增加，收入和利润同步增长。</t>
+    <t>产品销售业务增加，收入和利润同步增长。未达全年预算，还有9月月饼销售</t>
   </si>
   <si>
-    <t>东北销售宁波分计量项目预算执行分析（2026年07月）</t>
+    <t>东北销售宁波分计量项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>已完成</t>
@@ -689,10 +707,10 @@
     <t>目前此项目已终止</t>
   </si>
   <si>
-    <t>分析：该项目1-7月收入、成本、利润核算正常</t>
+    <t>分析：该项目1-8月收入、成本、利润核算正常</t>
   </si>
   <si>
-    <t>浙江衢州销售分公司配餐劳务项目预算执行分析（2026年07月）</t>
+    <t>浙江衢州销售分公司配餐劳务项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>该项目自4月起启动，运行相对稳定</t>
@@ -2724,7 +2742,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="4" tint="-0.25"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -3600,7 +3618,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>48</v>
       </c>
@@ -3609,16 +3627,20 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>50</v>
       </c>
@@ -3627,16 +3649,20 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="I4" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>52</v>
       </c>
@@ -3645,16 +3671,20 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="I5" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>53</v>
       </c>
@@ -3663,9 +3693,13 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -3825,9 +3859,13 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -3960,7 +3998,7 @@
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>78</v>
       </c>
@@ -3969,9 +4007,13 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="12" t="s">
+        <v>128</v>
+      </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
@@ -4014,7 +4056,7 @@
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>84</v>
       </c>
@@ -4023,9 +4065,13 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>119</v>
+      </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="12" t="s">
+        <v>119</v>
+      </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -4230,7 +4276,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>100</v>
       </c>
@@ -4239,9 +4285,13 @@
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -4266,7 +4316,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>103</v>
       </c>
@@ -4275,9 +4325,13 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -4305,7 +4359,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5058,7 +5112,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="4" tint="0.4"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -5073,7 +5127,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5143,11 +5197,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -5425,11 +5479,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -5519,11 +5573,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -5797,11 +5851,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -5837,11 +5891,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -5870,7 +5924,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5930,7 +5984,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>48</v>
       </c>
@@ -5939,9 +5993,13 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -6155,9 +6213,13 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -6191,16 +6253,20 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
@@ -6209,9 +6275,13 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>142</v>
+      </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>142</v>
+      </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -6290,7 +6360,7 @@
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>78</v>
       </c>
@@ -6299,9 +6369,13 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>143</v>
+      </c>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="12" t="s">
+        <v>143</v>
+      </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
@@ -6344,7 +6418,7 @@
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>84</v>
       </c>
@@ -6353,9 +6427,13 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>119</v>
+      </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="12" t="s">
+        <v>119</v>
+      </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -6560,7 +6638,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>100</v>
       </c>
@@ -6569,9 +6647,13 @@
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -6596,7 +6678,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>103</v>
       </c>
@@ -6605,9 +6687,13 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="12" t="s">
+        <v>137</v>
+      </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -6635,7 +6721,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7335,7 +7421,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -7373,7 +7459,7 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12"/>
@@ -7392,7 +7478,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="4" tint="0.4"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -7407,7 +7493,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7477,11 +7563,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -7759,11 +7845,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -7861,11 +7947,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -8135,11 +8221,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -8175,11 +8261,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -8196,7 +8282,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="3" tint="0.4"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -8211,7 +8297,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -8281,11 +8367,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -8303,11 +8389,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -8325,11 +8411,11 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -8347,11 +8433,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -8669,11 +8755,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -8727,11 +8813,11 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -8947,11 +9033,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -8987,11 +9073,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -9011,7 +9097,7 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="2" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="2" max="2" width="46.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9357,7 +9443,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10122,7 +10208,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10822,7 +10908,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -10860,7 +10946,7 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12"/>
@@ -10879,817 +10965,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
-  </sheetPr>
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="53" style="6" customWidth="1"/>
-    <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="27.2685185185185" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="30.5092592592593" customWidth="1"/>
-    <col min="10" max="14" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" ht="217" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-    </row>
-    <row r="6" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-    </row>
-    <row r="38" ht="180" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="H38" s="11"/>
-      <c r="I38" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-    </row>
-    <row r="40" ht="180" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="H40" s="11"/>
-      <c r="I40" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="3" tint="0.4"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -11704,7 +10980,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11764,7 +11040,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="180" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>48</v>
       </c>
@@ -11774,11 +11050,821 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+    </row>
+    <row r="6" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+    </row>
+    <row r="38" ht="198" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="12" t="s">
         <v>167</v>
+      </c>
+      <c r="H38" s="11"/>
+      <c r="I38" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+    </row>
+    <row r="40" ht="198" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="11"/>
+      <c r="I40" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.4"/>
+  </sheetPr>
+  <dimension ref="A1:N40"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="53" style="6" customWidth="1"/>
+    <col min="2" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
+    <col min="10" max="14" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -12140,7 +12226,7 @@
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>78</v>
       </c>
@@ -12150,11 +12236,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -12426,11 +12512,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -12466,11 +12552,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -12499,7 +12585,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -12559,7 +12645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>48</v>
       </c>
@@ -12568,9 +12654,13 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>173</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -12784,9 +12874,13 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -12820,9 +12914,13 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -12838,9 +12936,13 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -12919,7 +13021,7 @@
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>78</v>
       </c>
@@ -12928,9 +13030,13 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>170</v>
+      </c>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="12" t="s">
+        <v>170</v>
+      </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
@@ -12982,9 +13088,13 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -13189,7 +13299,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>100</v>
       </c>
@@ -13198,9 +13308,13 @@
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="12" t="s">
+        <v>174</v>
+      </c>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="12" t="s">
+        <v>174</v>
+      </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -13225,7 +13339,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>103</v>
       </c>
@@ -13234,9 +13348,13 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="12" t="s">
+        <v>174</v>
+      </c>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="12" t="s">
+        <v>174</v>
+      </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -13264,7 +13382,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -14017,7 +14135,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="4" tint="0.4"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -14032,7 +14150,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -14102,11 +14220,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -14532,11 +14650,11 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -14752,11 +14870,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -14792,11 +14910,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -14825,7 +14943,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -15590,7 +15708,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -15650,7 +15768,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>48</v>
       </c>
@@ -15659,9 +15777,13 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
+      <c r="G3" s="12" t="s">
+        <v>177</v>
+      </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>177</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -15875,9 +15997,13 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
+      <c r="G15" s="12" t="s">
+        <v>116</v>
+      </c>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
+      <c r="I15" s="12" t="s">
+        <v>116</v>
+      </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -15911,9 +16037,13 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="G17" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
+      <c r="I17" s="12" t="s">
+        <v>117</v>
+      </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -16019,9 +16149,13 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
+      <c r="G23" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
+      <c r="I23" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
@@ -16073,9 +16207,13 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>85</v>
+      </c>
       <c r="H26" s="11"/>
-      <c r="I26" s="12"/>
+      <c r="I26" s="12" t="s">
+        <v>85</v>
+      </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -16280,7 +16418,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>100</v>
       </c>
@@ -16289,9 +16427,13 @@
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+      <c r="G38" s="12" t="s">
+        <v>179</v>
+      </c>
       <c r="H38" s="11"/>
-      <c r="I38" s="12"/>
+      <c r="I38" s="12" t="s">
+        <v>179</v>
+      </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -16316,7 +16458,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>103</v>
       </c>
@@ -16325,9 +16467,13 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="12" t="s">
+        <v>179</v>
+      </c>
       <c r="H40" s="11"/>
-      <c r="I40" s="12"/>
+      <c r="I40" s="12" t="s">
+        <v>179</v>
+      </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -16341,6 +16487,834 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="3" tint="0.4"/>
+  </sheetPr>
+  <dimension ref="A1:N40"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="53" style="6" customWidth="1"/>
+    <col min="2" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="24.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="24.3333333333333" customWidth="1"/>
+    <col min="10" max="14" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H3" s="11"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+    </row>
+    <row r="11" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+    </row>
+    <row r="17" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+    </row>
+    <row r="23" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+    </row>
+    <row r="24" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+    </row>
+    <row r="25" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+    </row>
+    <row r="28" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H28" s="11"/>
+      <c r="I28" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="11"/>
+      <c r="I30" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34" s="11"/>
+      <c r="I34" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="H36" s="11"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+    </row>
+    <row r="38" ht="162" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="H38" s="11"/>
+      <c r="I38" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+    </row>
+    <row r="40" ht="162" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="H40" s="11"/>
+      <c r="I40" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -16355,7 +17329,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>176</v>
+        <v>34</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -16415,7 +17389,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>48</v>
       </c>
@@ -16425,17 +17399,19 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="H3" s="11"/>
-      <c r="I3" s="12"/>
+      <c r="I3" s="12" t="s">
+        <v>49</v>
+      </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>50</v>
       </c>
@@ -16444,10 +17420,12 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>178</v>
+        <v>51</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -16455,7 +17433,7 @@
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>52</v>
       </c>
@@ -16464,16 +17442,20 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="I5" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>53</v>
       </c>
@@ -16482,9 +17464,13 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
+      <c r="G6" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="I6" s="12" t="s">
+        <v>51</v>
+      </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -16500,9 +17486,13 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
+      <c r="G7" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
+      <c r="I7" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -16527,7 +17517,7 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>57</v>
       </c>
@@ -16536,9 +17526,13 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="G9" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -16554,16 +17548,20 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
+      <c r="I10" s="12" t="s">
+        <v>55</v>
+      </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
       <c r="N10" s="11"/>
     </row>
-    <row r="11" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>60</v>
       </c>
@@ -16573,11 +17571,11 @@
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="12" t="s">
-        <v>179</v>
+        <v>55</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="12" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11"/>
@@ -16630,9 +17628,7 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12" t="s">
-        <v>181</v>
-      </c>
+      <c r="G14" s="12"/>
       <c r="H14" s="11"/>
       <c r="I14" s="12"/>
       <c r="J14" s="11"/>
@@ -16641,7 +17637,7 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>64</v>
       </c>
@@ -16655,7 +17651,7 @@
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -16681,7 +17677,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>67</v>
       </c>
@@ -16691,11 +17687,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>184</v>
+        <v>68</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -16703,7 +17699,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
@@ -16712,9 +17708,13 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
+      <c r="I18" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -16731,11 +17731,11 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>185</v>
+        <v>72</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="12" t="s">
-        <v>185</v>
+        <v>72</v>
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
@@ -16770,16 +17770,20 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="12" t="s">
+        <v>75</v>
+      </c>
       <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
+      <c r="I21" s="12" t="s">
+        <v>75</v>
+      </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
       <c r="N21" s="11"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>76</v>
       </c>
@@ -16788,16 +17792,20 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
+      <c r="G22" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
+      <c r="I22" s="12" t="s">
+        <v>77</v>
+      </c>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
       <c r="N22" s="11"/>
     </row>
-    <row r="23" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>78</v>
       </c>
@@ -16807,11 +17815,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -16819,7 +17827,7 @@
       <c r="M23" s="11"/>
       <c r="N23" s="11"/>
     </row>
-    <row r="24" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>80</v>
       </c>
@@ -16829,11 +17837,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>188</v>
+        <v>81</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>188</v>
+        <v>81</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -16841,7 +17849,7 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>82</v>
       </c>
@@ -16851,11 +17859,11 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12" t="s">
-        <v>189</v>
+        <v>83</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12" t="s">
-        <v>189</v>
+        <v>83</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -16873,11 +17881,11 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -16903,7 +17911,7 @@
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
     </row>
-    <row r="28" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="90" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>87</v>
       </c>
@@ -16913,11 +17921,11 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -17029,11 +18037,11 @@
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="12" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="12" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -17059,7 +18067,7 @@
       <c r="M35" s="11"/>
       <c r="N35" s="11"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>97</v>
       </c>
@@ -17069,10 +18077,12 @@
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="12" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="H36" s="11"/>
-      <c r="I36" s="12"/>
+      <c r="I36" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
@@ -17097,7 +18107,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" ht="162" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="409.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>100</v>
       </c>
@@ -17107,11 +18117,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -17137,871 +18147,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" ht="162" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H40" s="11"/>
-      <c r="I40" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="4"/>
-  </sheetPr>
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="53" style="6" customWidth="1"/>
-    <col min="2" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="66.2592592592593" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="49.287037037037" customWidth="1"/>
-    <col min="10" max="14" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-    </row>
-    <row r="2" ht="45" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-    </row>
-    <row r="24" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-    </row>
-    <row r="25" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-    </row>
-    <row r="28" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="H34" s="11"/>
-      <c r="I34" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-    </row>
-    <row r="38" ht="288" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="H38" s="11"/>
-      <c r="I38" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-    </row>
-    <row r="40" ht="288" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="409.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>103</v>
       </c>
@@ -18032,7 +18178,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="3" tint="0.4"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -18047,7 +18193,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -18117,11 +18263,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -18139,11 +18285,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -18169,7 +18315,7 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" ht="38" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>53</v>
       </c>
@@ -18179,11 +18325,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -18227,7 +18373,7 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" ht="37" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>57</v>
       </c>
@@ -18237,11 +18383,11 @@
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="12" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="12" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J9" s="11"/>
       <c r="K9" s="11"/>
@@ -18349,11 +18495,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -18389,11 +18535,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -18765,7 +18911,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="11"/>
     </row>
-    <row r="38" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>100</v>
       </c>
@@ -18775,7 +18921,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
@@ -18805,7 +18951,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="11"/>
     </row>
-    <row r="40" ht="54" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" ht="72" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
         <v>103</v>
       </c>
@@ -18815,7 +18961,7 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
@@ -18836,7 +18982,7 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="3" tint="0.4"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -18851,7 +18997,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -18921,11 +19067,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -19199,7 +19345,7 @@
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -19559,11 +19705,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -19599,11 +19745,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -19620,7 +19766,7 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="3" tint="0.4"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -19635,7 +19781,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -19705,11 +19851,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -20077,11 +20223,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -20355,11 +20501,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -20395,11 +20541,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -20415,9 +20561,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="4"/>
-  </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
@@ -21236,7 +21379,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="4" tint="-0.25"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
@@ -24333,7 +24476,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="4"/>
+    <tabColor theme="4" tint="-0.25"/>
   </sheetPr>
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>

--- a/public/管理口径原因分析默认模版/浙江项目部.xlsx
+++ b/public/管理口径原因分析默认模版/浙江项目部.xlsx
@@ -9,35 +9,35 @@
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
     <sheet sheetId="3" name="合计" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="浙江销售分公司配餐业务" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="浙江湖州销售分公司配餐业务_合并" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="浙江湖州销售分公司配餐业务_222200150510" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="浙江湖州销售分公司配餐业务_222200150542" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="浙江湖州销售分公司配餐业务_SH3B26Z001" state="visible" r:id="rId10"/>
-    <sheet sheetId="9" name="浙江杭州销售分公司劳务输出_合并" state="visible" r:id="rId11"/>
-    <sheet sheetId="10" name="浙江杭州销售分公司劳务输出_222200150526" state="visible" r:id="rId12"/>
-    <sheet sheetId="11" name="浙江杭州销售分公司劳务输出_SH3B25Z076" state="visible" r:id="rId13"/>
-    <sheet sheetId="12" name="东北销售浙江宁波分公司配餐业务_合并" state="visible" r:id="rId14"/>
-    <sheet sheetId="13" name="东北销售浙江宁波分公司配餐业务_222200150527" state="visible" r:id="rId15"/>
-    <sheet sheetId="14" name="东北销售浙江宁波分公司配餐业务_SH3B26Z005" state="visible" r:id="rId16"/>
-    <sheet sheetId="15" name="东北销售浙江宁波分公司办公物业_合并" state="visible" r:id="rId17"/>
-    <sheet sheetId="16" name="东北销售浙江宁波分公司办公物业_222200150530" state="visible" r:id="rId18"/>
-    <sheet sheetId="17" name="东北销售浙江宁波分公司办公物业_SH3B26Z006" state="visible" r:id="rId19"/>
-    <sheet sheetId="18" name="浙江杭州地质研究院办公物业项目" state="visible" r:id="rId20"/>
-    <sheet sheetId="19" name="中石化天然气分公司浙江销售配餐项目_合并" state="visible" r:id="rId21"/>
-    <sheet sheetId="20" name="中石化天然气分公司浙江销售配餐项目_222200150535" state="visible" r:id="rId22"/>
-    <sheet sheetId="21" name="中石化天然气分公司浙江销售配餐项目_SH3B26Z002" state="visible" r:id="rId23"/>
-    <sheet sheetId="22" name="浙江杭州地质研究院配餐项目" state="visible" r:id="rId24"/>
-    <sheet sheetId="23" name="浙江绍兴销售分公司配餐劳务输出项目_合并" state="visible" r:id="rId25"/>
-    <sheet sheetId="24" name="浙江绍兴销售分公司配餐劳务输出项目_222200150540" state="visible" r:id="rId26"/>
-    <sheet sheetId="25" name="浙江绍兴销售分公司配餐劳务输出项目_SH3B26Z008" state="visible" r:id="rId27"/>
-    <sheet sheetId="26" name="浙江金华销售分公司配餐劳务输出项目_合并" state="visible" r:id="rId28"/>
-    <sheet sheetId="27" name="浙江金华销售分公司配餐劳务输出项目_222200150541" state="visible" r:id="rId29"/>
-    <sheet sheetId="28" name="浙江金华销售分公司配餐劳务输出项目_SH3B26Z004" state="visible" r:id="rId30"/>
-    <sheet sheetId="29" name="黄山阳光酒店分公司" state="visible" r:id="rId31"/>
-    <sheet sheetId="30" name="黄山项目部销售项目" state="visible" r:id="rId32"/>
-    <sheet sheetId="31" name="东北销售宁波分计量项目" state="visible" r:id="rId33"/>
-    <sheet sheetId="32" name="浙江衢州销售分公司配餐劳务项目" state="visible" r:id="rId34"/>
+    <sheet sheetId="4" name="浙江销售配餐" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="湖州配餐_合并" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="湖州配餐_222200150510" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="湖州配餐_222200150542" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="湖州配餐_SH3B26Z001" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="杭州劳务输出_合并" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="杭州劳务输出_222200150526" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="杭州劳务输出_SH3B25Z076" state="visible" r:id="rId13"/>
+    <sheet sheetId="12" name="东北浙江配餐_合并" state="visible" r:id="rId14"/>
+    <sheet sheetId="13" name="东北浙江配餐_222200150527" state="visible" r:id="rId15"/>
+    <sheet sheetId="14" name="东北浙江配餐_SH3B26Z005" state="visible" r:id="rId16"/>
+    <sheet sheetId="15" name="东北宁波物业_合并" state="visible" r:id="rId17"/>
+    <sheet sheetId="16" name="东北宁波物业_222200150530" state="visible" r:id="rId18"/>
+    <sheet sheetId="17" name="东北宁波物业_SH3B26Z006" state="visible" r:id="rId19"/>
+    <sheet sheetId="18" name="杭州地质物业" state="visible" r:id="rId20"/>
+    <sheet sheetId="19" name="中石化浙江配餐_合并" state="visible" r:id="rId21"/>
+    <sheet sheetId="20" name="中石化浙江配餐_222200150535" state="visible" r:id="rId22"/>
+    <sheet sheetId="21" name="中石化浙江配餐_SH3B26Z002" state="visible" r:id="rId23"/>
+    <sheet sheetId="22" name="杭州地质配餐" state="visible" r:id="rId24"/>
+    <sheet sheetId="23" name="绍兴劳务配餐_合并" state="visible" r:id="rId25"/>
+    <sheet sheetId="24" name="绍兴劳务配餐_222200150540" state="visible" r:id="rId26"/>
+    <sheet sheetId="25" name="绍兴劳务配餐_SH3B26Z008" state="visible" r:id="rId27"/>
+    <sheet sheetId="26" name="金华劳务配餐_合并" state="visible" r:id="rId28"/>
+    <sheet sheetId="27" name="金华劳务配餐_222200150541" state="visible" r:id="rId29"/>
+    <sheet sheetId="28" name="金华劳务配餐_SH3B26Z004" state="visible" r:id="rId30"/>
+    <sheet sheetId="29" name="黄山酒店租赁" state="visible" r:id="rId31"/>
+    <sheet sheetId="30" name="黄山销售" state="visible" r:id="rId32"/>
+    <sheet sheetId="31" name="东北宁波计量TERM" state="visible" r:id="rId33"/>
+    <sheet sheetId="32" name="浙江衢州配餐劳务" state="visible" r:id="rId34"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -61,91 +61,91 @@
     <t>合计</t>
   </si>
   <si>
-    <t>浙江销售分公司配餐业务</t>
+    <t>浙江销售配餐</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_合并</t>
+    <t>湖州配餐_合并</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_222200150510</t>
+    <t>湖州配餐_222200150510</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_222200150542</t>
+    <t>湖州配餐_222200150542</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_SH3B26Z001</t>
+    <t>湖州配餐_SH3B26Z001</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_合并</t>
+    <t>杭州劳务输出_合并</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_222200150526</t>
+    <t>杭州劳务输出_222200150526</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_SH3B25Z076</t>
+    <t>杭州劳务输出_SH3B25Z076</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_合并</t>
+    <t>东北浙江配餐_合并</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_222200150527</t>
+    <t>东北浙江配餐_222200150527</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_SH3B26Z005</t>
+    <t>东北浙江配餐_SH3B26Z005</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_合并</t>
+    <t>东北宁波物业_合并</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_222200150530</t>
+    <t>东北宁波物业_222200150530</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_SH3B26Z006</t>
+    <t>东北宁波物业_SH3B26Z006</t>
   </si>
   <si>
-    <t>浙江杭州地质研究院办公物业项目</t>
+    <t>杭州地质物业</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_合并</t>
+    <t>中石化浙江配餐_合并</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_222200150535</t>
+    <t>中石化浙江配餐_222200150535</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_SH3B26Z002</t>
+    <t>中石化浙江配餐_SH3B26Z002</t>
   </si>
   <si>
-    <t>浙江杭州地质研究院配餐项目</t>
+    <t>杭州地质配餐</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_合并</t>
+    <t>绍兴劳务配餐_合并</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_222200150540</t>
+    <t>绍兴劳务配餐_222200150540</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_SH3B26Z008</t>
+    <t>绍兴劳务配餐_SH3B26Z008</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_合并</t>
+    <t>金华劳务配餐_合并</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_222200150541</t>
+    <t>金华劳务配餐_222200150541</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_SH3B26Z004</t>
+    <t>金华劳务配餐_SH3B26Z004</t>
   </si>
   <si>
-    <t>黄山阳光酒店分公司</t>
+    <t>黄山酒店租赁</t>
   </si>
   <si>
-    <t>黄山项目部销售项目</t>
+    <t>黄山销售</t>
   </si>
   <si>
-    <t>东北销售宁波分计量项目</t>
+    <t>东北宁波计量TERM</t>
   </si>
   <si>
-    <t>浙江衢州销售分公司配餐劳务项目</t>
+    <t>浙江衢州配餐劳务</t>
   </si>
   <si>
     <t>合计预算执行分析（2026年08月）</t>
@@ -380,7 +380,7 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>浙江销售分公司配餐业务预算执行分析（2026年08月）</t>
+    <t>浙江销售配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>1-8月销售收入比同期有增长</t>
@@ -407,7 +407,7 @@
     <t>1-8月销售收入比同期有增长，成本相应有增加，利润有所增加，主要原因1、2月份及5月份发放甲方团购福利套餐，食材成本费用相对增加。2.春节前应甲方要求开展美食节，用餐人数增加，造成食材成本费用增加。3.后续严格管控食材成本，降本增效，提升对标利润率。此项目为季度结算，7-8月收入为预估收入，与实际结算有出入。</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_合并预算执行分析（2026年08月）</t>
+    <t>湖州配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>完成进度预算</t>
@@ -431,16 +431,16 @@
     <t>1-8月销售收入小幅增长，成本基本持平，导致利润也相应有所增加，其原因为：浙江湖州销售分公司配餐业务0031停掉后只经营劳务业务，故减少。</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_222200150510预算执行分析（2026年08月）</t>
+    <t>湖州配餐_222200150510预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_222200150542预算执行分析（2026年08月）</t>
+    <t>湖州配餐_222200150542预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江湖州销售分公司配餐业务_SH3B26Z001预算执行分析（2026年08月）</t>
+    <t>湖州配餐_SH3B26Z001预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_合并预算执行分析（2026年08月）</t>
+    <t>杭州劳务输出_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>此项目为季度结算，7-8月收入为预估收入，比去年同期有所增加</t>
@@ -458,13 +458,13 @@
     <t>1-8月收入较同期有所增加，成本有所减少。利润有所增加，主要原因是收入增加</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_222200150526预算执行分析（2026年08月）</t>
+    <t>杭州劳务输出_222200150526预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江杭州销售分公司劳务输出_SH3B25Z076预算执行分析（2026年08月）</t>
+    <t>杭州劳务输出_SH3B25Z076预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_合并预算执行分析（2026年08月）</t>
+    <t>东北浙江配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>今年用餐人数增加收入有所增加，食材费用随之增加，与该项目据实结算。</t>
@@ -476,16 +476,16 @@
     <t>该项目1-8月收入比去年同期有所增加，同时成本却比去年同期期有所增加，故利润有所增加，正常核算</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_222200150527预算执行分析（2026年08月）</t>
+    <t>东北浙江配餐_222200150527预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>需要和常州合并来分析</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司配餐业务_SH3B26Z005预算执行分析（2026年08月）</t>
+    <t>东北浙江配餐_SH3B26Z005预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_合并预算执行分析（2026年08月）</t>
+    <t>东北宁波物业_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>合同的物业费增加，故收入有所增加</t>
@@ -503,16 +503,16 @@
     <t>该项目1-8月收入，成本，利润有小幅增长。</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_222200150530预算执行分析（2026年08月）</t>
+    <t>东北宁波物业_222200150530预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>东北销售浙江宁波分公司办公物业_SH3B26Z006预算执行分析（2026年08月）</t>
+    <t>东北宁波物业_SH3B26Z006预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>已达标，继续保持</t>
   </si>
   <si>
-    <t>浙江杭州地质研究院办公物业项目预算执行分析（2026年08月）</t>
+    <t>杭州地质物业预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>物业费增加以及延展服务增加，且收入增加</t>
@@ -527,7 +527,7 @@
     <t>该项目部1-8月收入较去年同期大幅增加，利润也相应大幅增加主要原因为，今年1-8月的人工成本较去年小幅增长，但收入相应增加了许多。故利润有大幅增加。</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_合并预算执行分析（2026年08月）</t>
+    <t>中石化浙江配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>与去年同期相比。收入有小幅增加，目前运行稳定</t>
@@ -545,13 +545,13 @@
     <t>该项目1-8月利润上升的原因，主要是今年1-7月，人工成本有所减少</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_222200150535预算执行分析（2026年08月）</t>
+    <t>中石化浙江配餐_222200150535预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中石化天然气分公司浙江销售配餐项目_SH3B26Z002预算执行分析（2026年08月）</t>
+    <t>中石化浙江配餐_SH3B26Z002预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江杭州地质研究院配餐项目预算执行分析（2026年08月）</t>
+    <t>杭州地质配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>主要原因是收支结算周期不同导致，又因该项目是薪酬制，业主方力求服务好员工，故而压缩餐饮合同利润空间，所有损失在物业合同弥补。截止8月份末，餐卡余额同比增加，也影响本期利润。</t>
@@ -572,7 +572,7 @@
     <t>主要原因是收支结算周期不同导致，又因该项目是薪酬制，业主方力求服务好员工，故而压缩餐饮合同利润空间，所有损失在物业合同弥补。截止8月份末，餐卡余额同比增加，也影响本期利润。较去年同期有所增加</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_合并预算执行分析（2026年08月）</t>
+    <t>绍兴劳务配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>与上期基本平行，收入有小幅增加，运行稳定</t>
@@ -584,7 +584,7 @@
     <t>该项目1-8月收入、成本、利润与去年同期有小幅增加，已达标，继续保持</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_222200150540预算执行分析（2026年08月）</t>
+    <t>绍兴劳务配餐_222200150540预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>与上期基本平行，收入有小幅减少需要同常州合并来分析，运行稳定</t>
@@ -593,10 +593,10 @@
     <t>该项目1-8月收入、成本、利润与去年同期有小幅减少，需要 和常州核算合并来分析</t>
   </si>
   <si>
-    <t>浙江绍兴销售分公司配餐劳务输出项目_SH3B26Z008预算执行分析（2026年08月）</t>
+    <t>绍兴劳务配餐_SH3B26Z008预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_合并预算执行分析（2026年08月）</t>
+    <t>金华劳务配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>超过进度预算，加班费收入有所增加</t>
@@ -608,13 +608,13 @@
     <t>该项目1-8月收入、成本、利润与去年同期收入有所增加，主要是人工成本有所增加</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_222200150541预算执行分析（2026年08月）</t>
+    <t>金华劳务配餐_222200150541预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>浙江金华销售分公司配餐劳务输出项目_SH3B26Z004预算执行分析（2026年08月）</t>
+    <t>金华劳务配餐_SH3B26Z004预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>黄山阳光酒店分公司预算执行分析（2026年08月）</t>
+    <t>黄山酒店租赁预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>今年免租期较同期增加1个月，收入有所减少。</t>
@@ -668,7 +668,7 @@
     <t>利润减少原因：收入方面今年免租期较同期增加1个月，收入减少。成本方面1.房产税按从价方式计征较去年多1个月，增加成本约13万；2.相关人员下沉人工成本增加。</t>
   </si>
   <si>
-    <t>黄山项目部销售项目预算执行分析（2026年08月）</t>
+    <t>黄山销售预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>因销售具有不确定性，今年客户增加，销售额有所提升。</t>
@@ -698,7 +698,7 @@
     <t>产品销售业务增加，收入和利润同步增长。未达全年预算，还有9月月饼销售</t>
   </si>
   <si>
-    <t>东北销售宁波分计量项目预算执行分析（2026年08月）</t>
+    <t>东北宁波计量TERM预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>已完成</t>
@@ -710,7 +710,7 @@
     <t>分析：该项目1-8月收入、成本、利润核算正常</t>
   </si>
   <si>
-    <t>浙江衢州销售分公司配餐劳务项目预算执行分析（2026年08月）</t>
+    <t>浙江衢州配餐劳务预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>该项目自4月起启动，运行相对稳定</t>
@@ -9134,9 +9134,9 @@
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5">
-        <f>HYPERLINK("#'浙江销售分公司配餐业务'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C4" s="5" t="str">
+        <f>HYPERLINK("#'浙江销售配餐'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9144,9 +9144,9 @@
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5">
-        <f>HYPERLINK("#'浙江湖州销售分公司配餐业务_合并'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C5" s="5" t="str">
+        <f>HYPERLINK("#'湖州配餐_合并'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9154,9 +9154,9 @@
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="5">
-        <f>HYPERLINK("#'浙江湖州销售分公司配餐业务_222200150510'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C6" s="5" t="str">
+        <f>HYPERLINK("#'湖州配餐_222200150510'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9164,9 +9164,9 @@
       <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="5">
-        <f>HYPERLINK("#'浙江湖州销售分公司配餐业务_222200150542'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C7" s="5" t="str">
+        <f>HYPERLINK("#'湖州配餐_222200150542'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9174,9 +9174,9 @@
       <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <f>HYPERLINK("#'浙江湖州销售分公司配餐业务_SH3B26Z001'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C8" s="5" t="str">
+        <f>HYPERLINK("#'湖州配餐_SH3B26Z001'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9184,9 +9184,9 @@
       <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="5">
-        <f>HYPERLINK("#'浙江杭州销售分公司劳务输出_合并'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C9" s="5" t="str">
+        <f>HYPERLINK("#'杭州劳务输出_合并'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9194,9 +9194,9 @@
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="5">
-        <f>HYPERLINK("#'浙江杭州销售分公司劳务输出_222200150526'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C10" s="5" t="str">
+        <f>HYPERLINK("#'杭州劳务输出_222200150526'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9204,9 +9204,9 @@
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="5">
-        <f>HYPERLINK("#'浙江杭州销售分公司劳务输出_SH3B25Z076'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C11" s="5" t="str">
+        <f>HYPERLINK("#'杭州劳务输出_SH3B25Z076'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9214,9 +9214,9 @@
       <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="5">
-        <f>HYPERLINK("#'东北销售浙江宁波分公司配餐业务_合并'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C12" s="5" t="str">
+        <f>HYPERLINK("#'东北浙江配餐_合并'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9224,9 +9224,9 @@
       <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="5">
-        <f>HYPERLINK("#'东北销售浙江宁波分公司配餐业务_222200150527'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C13" s="5" t="str">
+        <f>HYPERLINK("#'东北浙江配餐_222200150527'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9234,9 +9234,9 @@
       <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="5">
-        <f>HYPERLINK("#'东北销售浙江宁波分公司配餐业务_SH3B26Z005'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C14" s="5" t="str">
+        <f>HYPERLINK("#'东北浙江配餐_SH3B26Z005'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9244,9 +9244,9 @@
       <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="5">
-        <f>HYPERLINK("#'东北销售浙江宁波分公司办公物业_合并'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C15" s="5" t="str">
+        <f>HYPERLINK("#'东北宁波物业_合并'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9254,9 +9254,9 @@
       <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="5">
-        <f>HYPERLINK("#'东北销售浙江宁波分公司办公物业_222200150530'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C16" s="5" t="str">
+        <f>HYPERLINK("#'东北宁波物业_222200150530'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9264,9 +9264,9 @@
       <c r="B17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="5">
-        <f>HYPERLINK("#'东北销售浙江宁波分公司办公物业_SH3B26Z006'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C17" s="5" t="str">
+        <f>HYPERLINK("#'东北宁波物业_SH3B26Z006'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9274,9 +9274,9 @@
       <c r="B18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="5">
-        <f>HYPERLINK("#'浙江杭州地质研究院办公物业项目'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C18" s="5" t="str">
+        <f>HYPERLINK("#'杭州地质物业'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9284,9 +9284,9 @@
       <c r="B19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="5">
-        <f>HYPERLINK("#'中石化天然气分公司浙江销售配餐项目_合并'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C19" s="5" t="str">
+        <f>HYPERLINK("#'中石化浙江配餐_合并'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9294,9 +9294,9 @@
       <c r="B20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="5">
-        <f>HYPERLINK("#'中石化天然气分公司浙江销售配餐项目_222200150535'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C20" s="5" t="str">
+        <f>HYPERLINK("#'中石化浙江配餐_222200150535'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9304,9 +9304,9 @@
       <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5">
-        <f>HYPERLINK("#'中石化天然气分公司浙江销售配餐项目_SH3B26Z002'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C21" s="5" t="str">
+        <f>HYPERLINK("#'中石化浙江配餐_SH3B26Z002'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9314,9 +9314,9 @@
       <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="5">
-        <f>HYPERLINK("#'浙江杭州地质研究院配餐项目'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C22" s="5" t="str">
+        <f>HYPERLINK("#'杭州地质配餐'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9324,9 +9324,9 @@
       <c r="B23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="5">
-        <f>HYPERLINK("#'浙江绍兴销售分公司配餐劳务输出项目_合并'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C23" s="5" t="str">
+        <f>HYPERLINK("#'绍兴劳务配餐_合并'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9334,9 +9334,9 @@
       <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="5">
-        <f>HYPERLINK("#'浙江绍兴销售分公司配餐劳务输出项目_222200150540'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C24" s="5" t="str">
+        <f>HYPERLINK("#'绍兴劳务配餐_222200150540'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9344,9 +9344,9 @@
       <c r="B25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="5">
-        <f>HYPERLINK("#'浙江绍兴销售分公司配餐劳务输出项目_SH3B26Z008'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C25" s="5" t="str">
+        <f>HYPERLINK("#'绍兴劳务配餐_SH3B26Z008'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9354,9 +9354,9 @@
       <c r="B26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="5">
-        <f>HYPERLINK("#'浙江金华销售分公司配餐劳务输出项目_合并'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C26" s="5" t="str">
+        <f>HYPERLINK("#'金华劳务配餐_合并'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9364,9 +9364,9 @@
       <c r="B27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="5">
-        <f>HYPERLINK("#'浙江金华销售分公司配餐劳务输出项目_222200150541'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C27" s="5" t="str">
+        <f>HYPERLINK("#'金华劳务配餐_222200150541'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9374,9 +9374,9 @@
       <c r="B28" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="5">
-        <f>HYPERLINK("#'浙江金华销售分公司配餐劳务输出项目_SH3B26Z004'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C28" s="5" t="str">
+        <f>HYPERLINK("#'金华劳务配餐_SH3B26Z004'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9384,9 +9384,9 @@
       <c r="B29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="5">
-        <f>HYPERLINK("#'黄山阳光酒店分公司'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C29" s="5" t="str">
+        <f>HYPERLINK("#'黄山酒店租赁'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9394,9 +9394,9 @@
       <c r="B30" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <f>HYPERLINK("#'黄山项目部销售项目'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C30" s="5" t="str">
+        <f>HYPERLINK("#'黄山销售'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9404,9 +9404,9 @@
       <c r="B31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="5">
-        <f>HYPERLINK("#'东北销售宁波分计量项目'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C31" s="5" t="str">
+        <f>HYPERLINK("#'东北宁波计量TERM'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9414,9 +9414,9 @@
       <c r="B32" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="5">
-        <f>HYPERLINK("#'浙江衢州销售分公司配餐劳务项目'!A1","点击跳转 ➔")</f>
-        <v>0</v>
+      <c r="C32" s="5" t="str">
+        <f>HYPERLINK("#'浙江衢州配餐劳务'!A1","点击跳转 ➔")</f>
+        <v>点击跳转 ➔</v>
       </c>
     </row>
   </sheetData>
